--- a/docs/수입신고서_항목매핑표.xlsx
+++ b/docs/수입신고서_항목매핑표.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>⚠️부분(73%)</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2167,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -2498,12 +2498,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -2957,12 +2957,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -3129,12 +3129,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -3172,12 +3172,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -3215,12 +3215,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>⚠️부분(92%)</t>
         </is>
       </c>
     </row>
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -3717,12 +3717,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -3986,12 +3986,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>
@@ -4661,12 +4661,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>❌공백</t>
+          <t>✅충족</t>
         </is>
       </c>
     </row>

--- a/docs/수입신고서_항목매핑표.xlsx
+++ b/docs/수입신고서_항목매핑표.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>import_declarations.overseas_supplier_country</t>
+          <t>import_declarations.overseas_supplier_country_code</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>import_declarations.departure_country</t>
+          <t>import_declarations.departure_country_code</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>import_declaration_items.origin_country</t>
+          <t>import_declaration_items.origin_country_code</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G157" t="inlineStr"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G158" t="inlineStr"/>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G183" t="inlineStr"/>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G190" t="inlineStr"/>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G195" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G197" t="inlineStr"/>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G211" t="inlineStr"/>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
